--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2021-11-25</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2022-01-27</t>
+          <t>2022-01-28</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2023-04-24</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2022-03-08</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2022-04-19</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2022-01-03</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-11-27</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2023-02-21</t>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2022-01-11</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2022-01-11</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17875,7 +17875,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18565,7 +18565,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18751,7 +18751,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18813,7 +18813,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19317,7 +19317,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2022-09-19</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20813,7 +20813,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21751,7 +21751,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-12-17</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="E339" s="4" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
@@ -21813,14 +21813,14 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
         <v>8043200</v>
       </c>
       <c r="I339" s="5" t="n">
-        <v>33100</v>
+        <v>33236</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>8043200</v>
       </c>
       <c r="L339" s="5" t="n">
-        <v>33100</v>
+        <v>33236</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2023-03-03</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22296,7 +22296,7 @@
           <t>A | 1000呎 (4+房)
 $4300万
 $43,000/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -22304,7 +22304,7 @@
           <t>B | 566呎 (2房)
 $2434万
 $43,000/呎
-(23年-06月-15日)</t>
+(23年-06月-16日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -22312,7 +22312,7 @@
           <t>C | 796呎 (3房)
 $3224万
 $40,500/呎
-(23年-04月-25日)</t>
+(23年-04月-26日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -22320,7 +22320,7 @@
           <t>D | 880呎 (3房)
 $3524万
 $40,045/呎
-(24年-05月-08日)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -22352,7 +22352,7 @@
           <t>B | 287呎 (1房)
 $951万
 $33,136/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -22360,7 +22360,7 @@
           <t>C | 456呎 (2房)
 $1520万
 $33,341/呎
-(23年-04月-15日)</t>
+(23年-04月-16日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -22368,7 +22368,7 @@
           <t>D | 332呎 (1房)
 $1035万
 $31,164/呎
-(23年-03月-29日)</t>
+(23年-03月-30日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -22384,7 +22384,7 @@
           <t>F | 265呎 (开放式)
 $811万
 $30,617/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -22392,7 +22392,7 @@
           <t>G | 292呎 (1房)
 $902万
 $30,896/呎
-(23年-06月-25日)</t>
+(23年-06月-26日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -22400,7 +22400,7 @@
           <t>H | 228呎 (开放式)
 $742万
 $32,526/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -22408,7 +22408,7 @@
           <t>J | 288呎 (1房)
 $890万
 $30,909/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -22416,7 +22416,7 @@
           <t>K | 298呎 (1房)
 $870万
 $29,208/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -22424,7 +22424,7 @@
           <t>L | 302呎 (1房)
 $973万
 $32,206/呎
-(21年-11月-25日)</t>
+(21年-11月-26日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -22432,7 +22432,7 @@
           <t>M | 293呎 (1房)
 $963万
 $32,870/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -22440,7 +22440,7 @@
           <t>N | 300呎 (1房)
 $962万
 $32,074/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -22463,7 +22463,7 @@
           <t>B | 287呎 (1房)
 $946万
 $32,976/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -22471,7 +22471,7 @@
           <t>C | 456呎 (2房)
 $1468万
 $32,200/呎
-(22年-05月-10日)</t>
+(22年-05月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -22479,7 +22479,7 @@
           <t>D | 332呎 (1房)
 $1030万
 $31,009/呎
-(23年-03月-20日)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -22495,7 +22495,7 @@
           <t>F | 265呎 (开放式)
 $806万
 $30,426/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -22503,7 +22503,7 @@
           <t>G | 292呎 (1房)
 $898万
 $30,742/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -22511,7 +22511,7 @@
           <t>H | 228呎 (开放式)
 $740万
 $32,471/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -22519,7 +22519,7 @@
           <t>J | 288呎 (1房)
 $886万
 $30,759/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -22527,7 +22527,7 @@
           <t>K | 299呎 (1房)
 $885万
 $29,609/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -22535,7 +22535,7 @@
           <t>L | 302呎 (1房)
 $968万
 $32,057/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -22543,7 +22543,7 @@
           <t>M | 293呎 (1房)
 $958万
 $32,707/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -22551,7 +22551,7 @@
           <t>N | 301呎 (1房)
 $957万
 $31,809/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
           <t>B | 286呎 (1房)
 $921万
 $32,214/呎
-(23年-04月-12日)</t>
+(23年-04月-13日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -22582,7 +22582,7 @@
           <t>C | 456呎 (2房)
 $1433万
 $31,421/呎
-(22年-02月-21日)</t>
+(22年-02月-22日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -22590,7 +22590,7 @@
           <t>D | 333呎 (1房)
 $1047万
 $31,448/呎
-(22年-01月-27日)</t>
+(22年-01月-28日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -22606,7 +22606,7 @@
           <t>F | 265呎 (开放式)
 $803万
 $30,315/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -22614,7 +22614,7 @@
           <t>G | 292呎 (1房)
 $893万
 $30,591/呎
-(23年-03月-27日)</t>
+(23年-03月-28日)</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -22630,7 +22630,7 @@
           <t>J | 288呎 (1房)
 $882万
 $30,609/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -22638,7 +22638,7 @@
           <t>K | 298呎 (1房)
 $881万
 $29,560/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -22646,7 +22646,7 @@
           <t>L | 302呎 (1房)
 $964万
 $31,904/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -22654,7 +22654,7 @@
           <t>M | 293呎 (1房)
 $954万
 $32,544/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -22662,7 +22662,7 @@
           <t>N | 300呎 (1房)
 $932万
 $31,065/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
           <t>B | 286呎 (1房)
 $932万
 $32,594/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -22693,7 +22693,7 @@
           <t>C | 456呎 (2房)
 $1408万
 $30,876/呎
-(22年-02月-03日)</t>
+(22年-02月-04日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -22701,7 +22701,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月-10日)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -22717,7 +22717,7 @@
           <t>F | 265呎 (开放式)
 $799万
 $30,162/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -22725,7 +22725,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(23年-04月-23日)</t>
+(23年-04月-24日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -22733,7 +22733,7 @@
           <t>H | 228呎 (开放式)
 $733万
 $32,147/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -22741,7 +22741,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -22749,7 +22749,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -22757,7 +22757,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月-20日)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -22765,7 +22765,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -22773,7 +22773,7 @@
           <t>N | 300呎 (1房)
 $948万
 $31,599/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -22796,7 +22796,7 @@
           <t>B | 287呎 (1房)
 $917万
 $31,948/呎
-(23年-07月-05日)</t>
+(23年-07月-06日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -22804,7 +22804,7 @@
           <t>C | 456呎 (2房)
 $1357万
 $29,761/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -22812,7 +22812,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,703/呎
-(23年-04月-19日)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -22820,7 +22820,7 @@
           <t>E | 262呎 (开放式)
 $876万
 $33,454/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -22828,7 +22828,7 @@
           <t>F | 264呎 (开放式)
 $817万
 $30,949/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -22836,7 +22836,7 @@
           <t>G | 292呎 (1房)
 $889万
 $30,437/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -22844,7 +22844,7 @@
           <t>H | 228呎 (开放式)
 $770万
 $33,758/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -22852,7 +22852,7 @@
           <t>J | 288呎 (1房)
 $877万
 $30,462/呎
-(21年-12月-28日)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -22860,7 +22860,7 @@
           <t>K | 298呎 (1房)
 $877万
 $29,415/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -22868,7 +22868,7 @@
           <t>L | 302呎 (1房)
 $959万
 $31,755/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -22876,7 +22876,7 @@
           <t>M | 293呎 (1房)
 $949万
 $32,382/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -22884,7 +22884,7 @@
           <t>N | 301呎 (1房)
 $948万
 $31,494/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -22907,7 +22907,7 @@
           <t>B | 286呎 (1房)
 $907万
 $31,717/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -22915,7 +22915,7 @@
           <t>C | 456呎 (2房)
 $1339万
 $29,366/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -22923,7 +22923,7 @@
           <t>D | 333呎 (1房)
 $1011万
 $30,370/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
@@ -22939,7 +22939,7 @@
           <t>F | 265呎 (开放式)
 $791万
 $29,843/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -22947,7 +22947,7 @@
           <t>G | 292呎 (1房)
 $880万
 $30,135/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I11" s="24" t="inlineStr">
@@ -22963,7 +22963,7 @@
           <t>J | 288呎 (1房)
 $869万
 $30,168/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -22971,7 +22971,7 @@
           <t>K | 299呎 (1房)
 $852万
 $28,511/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -22979,7 +22979,7 @@
           <t>L | 302呎 (1房)
 $934万
 $30,924/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -22987,7 +22987,7 @@
           <t>M | 293呎 (1房)
 $939万
 $32,059/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -22995,7 +22995,7 @@
           <t>N | 300呎 (1房)
 $938万
 $31,283/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
           <t>B | 286呎 (1房)
 $903万
 $31,563/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -23026,7 +23026,7 @@
           <t>C | 456呎 (2房)
 $1365万
 $29,928/呎
-(21年-12月-20日)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -23034,7 +23034,7 @@
           <t>D | 332呎 (1房)
 $1019万
 $30,679/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -23050,7 +23050,7 @@
           <t>F | 265呎 (开放式)
 $804万
 $30,353/呎
-(22年-03月-08日)</t>
+(22年-03月-09日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -23058,7 +23058,7 @@
           <t>G | 292呎 (1房)
 $875万
 $29,965/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -23066,7 +23066,7 @@
           <t>H | 228呎 (开放式)
 $726万
 $31,839/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -23074,7 +23074,7 @@
           <t>J | 288呎 (1房)
 $841万
 $29,203/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -23082,7 +23082,7 @@
           <t>K | 298呎 (1房)
 $830万
 $27,846/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -23090,7 +23090,7 @@
           <t>L | 302呎 (1房)
 $909万
 $30,108/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -23098,7 +23098,7 @@
           <t>M | 293呎 (1房)
 $935万
 $31,899/呎
-(23年-12月-14日)</t>
+(23年-12月-15日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23106,7 +23106,7 @@
           <t>N | 300呎 (1房)
 $934万
 $31,130/呎
-(21年-12月-20日)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
           <t>B | 287呎 (1房)
 $898万
 $31,302/呎
-(23年-05月-08日)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -23137,7 +23137,7 @@
           <t>C | 456呎 (2房)
 $1391万
 $30,511/呎
-(22年-02月-13日)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -23145,7 +23145,7 @@
           <t>D | 332呎 (1房)
 $1013万
 $30,526/呎
-(21年-12月-08日)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -23153,7 +23153,7 @@
           <t>E | 262呎 (开放式)
 $779万
 $29,717/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -23161,7 +23161,7 @@
           <t>F | 265呎 (开放式)
 $796万
 $30,054/呎
-(21年-11月-19日)</t>
+(21年-11月-20日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -23169,7 +23169,7 @@
           <t>G | 292呎 (1房)
 $866万
 $29,641/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -23177,7 +23177,7 @@
           <t>H | 228呎 (开放式)
 $711万
 $31,164/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -23185,7 +23185,7 @@
           <t>J | 288呎 (1房)
 $819万
 $28,428/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -23193,7 +23193,7 @@
           <t>K | 298呎 (1房)
 $826万
 $27,710/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -23201,7 +23201,7 @@
           <t>L | 302呎 (1房)
 $925万
 $30,634/呎
-(21年-12月-20日)</t>
+(21年-12月-21日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -23209,7 +23209,7 @@
           <t>M | 292呎 (1房)
 $941万
 $32,219/呎
-(23年-05月-08日)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -23217,7 +23217,7 @@
           <t>N | 301呎 (1房)
 $929万
 $30,870/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -23240,7 +23240,7 @@
           <t>B | 287呎 (1房)
 $894万
 $31,149/呎
-(23年-06月-06日)</t>
+(23年-06月-07日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -23248,7 +23248,7 @@
           <t>C | 456呎 (2房)
 $1367万
 $29,975/呎
-(22年-01月-16日)</t>
+(22年-01月-17日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -23256,7 +23256,7 @@
           <t>D | 332呎 (1房)
 $1008万
 $30,374/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23264,7 +23264,7 @@
           <t>E | 262呎 (开放式)
 $775万
 $29,569/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -23272,7 +23272,7 @@
           <t>F | 265呎 (开放式)
 $792万
 $29,905/呎
-(21年-12月-08日)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -23280,7 +23280,7 @@
           <t>G | 292呎 (1房)
 $861万
 $29,497/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -23288,7 +23288,7 @@
           <t>H | 228呎 (开放式)
 $687万
 $30,146/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -23296,7 +23296,7 @@
           <t>J | 288呎 (1房)
 $833万
 $28,916/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -23304,7 +23304,7 @@
           <t>K | 298呎 (1房)
 $840万
 $28,183/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -23312,7 +23312,7 @@
           <t>L | 302呎 (1房)
 $921万
 $30,488/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -23320,7 +23320,7 @@
           <t>M | 293呎 (1房)
 $916万
 $31,254/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23328,7 +23328,7 @@
           <t>N | 301呎 (1房)
 $925万
 $30,718/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -23351,7 +23351,7 @@
           <t>B | 287呎 (1房)
 $885万
 $30,826/呎
-(22年-04月-19日)</t>
+(22年-04月-20日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -23359,7 +23359,7 @@
           <t>C | 456呎 (2房)
 $1323万
 $29,015/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -23367,7 +23367,7 @@
           <t>D | 332呎 (1房)
 $992万
 $29,865/呎
-(21年-12月-22日)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -23375,7 +23375,7 @@
           <t>E | 262呎 (开放式)
 $771万
 $29,422/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -23383,7 +23383,7 @@
           <t>F | 264呎 (开放式)
 $771万
 $29,219/呎
-(21年-12月-22日)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -23391,7 +23391,7 @@
           <t>G | 292呎 (1房)
 $857万
 $29,349/呎
-(22年-06月-08日)</t>
+(22年-06月-09日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -23399,7 +23399,7 @@
           <t>H | 228呎 (开放式)
 $684万
 $29,996/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -23407,7 +23407,7 @@
           <t>J | 288呎 (1房)
 $829万
 $28,769/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -23415,7 +23415,7 @@
           <t>K | 299呎 (1房)
 $836万
 $27,947/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -23423,7 +23423,7 @@
           <t>L | 302呎 (1房)
 $867万
 $28,721/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -23431,7 +23431,7 @@
           <t>M | 293呎 (1房)
 $888万
 $30,311/呎
-(24年-02月-28日)</t>
+(24年-02月-29日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23439,7 +23439,7 @@
           <t>N | 300呎 (1房)
 $907万
 $30,231/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -23462,7 +23462,7 @@
           <t>B | 287呎 (1房)
 $883万
 $30,767/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -23470,7 +23470,7 @@
           <t>C | 456呎 (2房)
 $1294万
 $28,370/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -23478,7 +23478,7 @@
           <t>D | 332呎 (1房)
 $989万
 $29,797/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -23486,7 +23486,7 @@
           <t>E | 262呎 (开放式)
 $767万
 $29,277/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -23494,7 +23494,7 @@
           <t>F | 265呎 (开放式)
 $785万
 $29,610/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -23502,7 +23502,7 @@
           <t>G | 292呎 (1房)
 $872万
 $29,853/呎
-(22年-06月-07日)</t>
+(22年-06月-08日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -23510,7 +23510,7 @@
           <t>H | 228呎 (开放式)
 $680万
 $29,846/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -23518,7 +23518,7 @@
           <t>J | 288呎 (1房)
 $824万
 $28,628/呎
-(21年-12月-21日)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -23526,7 +23526,7 @@
           <t>K | 298呎 (1房)
 $831万
 $27,902/呎
-(21年-12月-21日)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -23534,7 +23534,7 @@
           <t>L | 302呎 (1房)
 $846万
 $28,017/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -23542,7 +23542,7 @@
           <t>M | 293呎 (1房)
 $870万
 $29,706/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -23550,7 +23550,7 @@
           <t>N | 301呎 (1房)
 $894万
 $29,690/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -23573,7 +23573,7 @@
           <t>B | 287呎 (1房)
 $879万
 $30,616/呎
-(22年-01月-05日)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -23581,7 +23581,7 @@
           <t>C | 456呎 (2房)
 $1290万
 $28,285/呎
-(22年-01月-03日)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -23589,7 +23589,7 @@
           <t>D | 332呎 (1房)
 $953万
 $28,705/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -23597,7 +23597,7 @@
           <t>E | 262呎 (开放式)
 $801万
 $30,586/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -23605,7 +23605,7 @@
           <t>F | 264呎 (开放式)
 $764万
 $28,930/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -23613,7 +23613,7 @@
           <t>G | 292呎 (1房)
 $863万
 $29,540/呎
-(23年-12月-13日)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -23621,7 +23621,7 @@
           <t>H | 228呎 (开放式)
 $677万
 $29,700/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -23629,7 +23629,7 @@
           <t>J | 288呎 (1房)
 $802万
 $27,847/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -23637,7 +23637,7 @@
           <t>K | 298呎 (1房)
 $809万
 $27,142/呎
-(21年-11月-19日)</t>
+(21年-11月-20日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -23645,7 +23645,7 @@
           <t>L | 302呎 (1房)
 $842万
 $27,877/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -23653,7 +23653,7 @@
           <t>M | 293呎 (1房)
 $866万
 $29,559/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23661,7 +23661,7 @@
           <t>N | 301呎 (1房)
 $870万
 $28,902/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
           <t>B | 287呎 (1房)
 $874万
 $30,469/呎
-(21年-11月-27日)</t>
+(21年-11月-28日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -23692,7 +23692,7 @@
           <t>C | 456呎 (2房)
 $1354万
 $29,692/呎
-(22年-05月-24日)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -23700,7 +23700,7 @@
           <t>D | 332呎 (1房)
 $969万
 $29,199/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -23708,7 +23708,7 @@
           <t>E | 262呎 (开放式)
 $797万
 $30,435/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -23716,7 +23716,7 @@
           <t>F | 264呎 (开放式)
 $777万
 $29,426/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -23724,7 +23724,7 @@
           <t>G | 292呎 (1房)
 $844万
 $28,911/呎
-(23年-08月-21日)</t>
+(23年-08月-22日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -23732,10 +23732,121 @@
           <t>H | 228呎 (开放式)
 $674万
 $29,550/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$816万
+$28,325/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$823万
+$27,517/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$820万
+$27,137/呎
+(21年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$862万
+$29,411/呎
+(25年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$885万
+$29,495/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$855万
+$29,807/呎
+(22年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1354万
+$29,692/呎
+(22年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$969万
+$29,199/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$797万
+$30,435/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$777万
+$29,426/呎
+(21年-12月-20日)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$844万
+$28,911/呎
+(25年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$694万
+$30,438/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
 $816万
@@ -23743,46 +23854,46 @@
 (21年-12月-09日)</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
 $823万
-$27,517/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
+$27,609/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
-$820万
-$27,137/呎
-(21年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr">
+$838万
+$27,740/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
 $862万
 $29,411/呎
-(25年-12月-03日)</t>
-        </is>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
 $885万
-$29,495/呎
+$29,397/呎
 (21年-12月-13日)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -23790,110 +23901,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$844万
+$29,523/呎
+(21年-12月-22日)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1313万
+$28,788/呎
+(23年-02月-22日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$965万
+$29,071/呎
+(21年-12月-22日)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$786万
+$29,992/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$746万
+$28,264/呎
+(23年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$816万
+$27,949/呎
+(22年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$664万
+$29,112/呎
+(26年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$789万
+$27,408/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$810万
+$27,104/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$825万
+$27,326/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$824万
+$28,115/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
 $855万
-$29,807/呎
-(22年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1354万
-$29,692/呎
-(22年-08月-16日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$969万
-$29,199/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$797万
-$30,435/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$777万
-$29,426/呎
-(21年-12月-19日)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$844万
-$28,911/呎
-(25年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$694万
-$30,438/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$816万
-$28,325/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$823万
-$27,609/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$838万
-$27,740/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="M19" s="20" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$862万
-$29,411/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$885万
-$29,397/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
+$28,398/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -23901,110 +24012,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$844万
-$29,523/呎
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$822万
+$28,637/呎
 (21年-12月-21日)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
-$1313万
-$28,788/呎
-(23年-02月-21日)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
+$1309万
+$28,703/呎
+(23年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 332呎 (1房)
-$965万
-$29,071/呎
-(21年-12月-21日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
+$950万
+$28,620/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$786万
-$29,992/呎
-(26年-03月-26日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$746万
-$28,264/呎
-(23年-04月-12日)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
+$730万
+$27,859/呎
+(26年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$730万
+$27,557/呎
+(25年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$816万
-$27,949/呎
-(22年-08月-16日)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
+$812万
+$27,811/呎
+(23年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 228呎 (开放式)
-$664万
-$29,112/呎
-(26年-01月-14日)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
+$646万
+$28,354/呎
+(26年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
-$789万
-$27,408/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr">
+$785万
+$27,271/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 299呎 (1房)
-$810万
-$27,104/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
+$806万
+$26,969/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
-$825万
-$27,326/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="M20" s="20" t="inlineStr">
+$821万
+$27,189/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
-$824万
-$28,115/呎
-(24年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$855万
-$28,398/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
+$835万
+$28,499/呎
+(24年-02月-19日)</t>
+        </is>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$850万
+$28,348/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24012,110 +24123,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 287呎 (1房)
-$822万
-$28,637/呎
+$818万
+$28,493/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1295万
+$28,399/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$945万
+$28,476/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$789万
+$30,116/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$743万
+$28,030/呎
+(21年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$808万
+$27,672/呎
+(23年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$644万
+$28,255/呎
+(25年-12月-29日)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$781万
+$27,133/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$802万
+$26,924/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$799万
+$26,467/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$819万
+$27,949/呎
+(23年-05月-30日)</t>
+        </is>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
+$846万
+$28,113/呎
 (21年-12月-20日)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1309万
-$28,703/呎
-(23年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$950万
-$28,620/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$730万
-$27,859/呎
-(26年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$730万
-$27,557/呎
-(25年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$812万
-$27,811/呎
-(23年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$646万
-$28,354/呎
-(26年-01月-04日)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$785万
-$27,271/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$806万
-$26,969/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$821万
-$27,189/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="M21" s="20" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$835万
-$28,499/呎
-(24年-02月-18日)</t>
-        </is>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$850万
-$28,348/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24123,110 +24234,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$818万
-$28,493/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$832万
+$29,083/呎
+(21年-12月-20日)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
-$1295万
-$28,399/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$945万
-$28,476/呎
+$1291万
+$28,312/呎
+(22年-01月-11日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$951万
+$28,556/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$723万
+$27,581/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$739万
+$27,888/呎
 (21年-12月-13日)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$789万
-$30,116/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$743万
-$28,030/呎
-(21年-12月-14日)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$808万
-$27,672/呎
-(23年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+$804万
+$27,533/呎
+(23年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 228呎 (开放式)
-$644万
-$28,255/呎
-(25年-12月-28日)</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
+$640万
+$28,069/呎
+(25年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
-$781万
-$27,133/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
+$778万
+$26,999/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 298呎 (1房)
-$802万
-$26,924/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
+$798万
+$26,791/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
-$799万
-$26,467/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="M22" s="20" t="inlineStr">
+$813万
+$26,918/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
 $819万
-$27,949/呎
-(23年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
+$27,940/呎
+(25年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 301呎 (1房)
-$846万
-$28,113/呎
-(21年-12月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
+$842万
+$27,973/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24234,110 +24345,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$832万
-$29,083/呎
-(21年-12月-19日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$828万
+$28,837/呎
+(21年-12月-21日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
-$1291万
-$28,312/呎
-(22年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
+$1287万
+$28,227/呎
+(22年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 333呎 (1房)
-$951万
-$28,556/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
+$916万
+$27,497/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$723万
-$27,581/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
+$735万
+$28,053/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 265呎 (开放式)
-$739万
-$27,888/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
+$719万
+$27,146/呎
+(21年-11月-20日)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$804万
-$27,533/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+$800万
+$27,395/呎
+(23年-06月-19日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 228呎 (开放式)
-$640万
-$28,069/呎
-(25年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
+$652万
+$28,596/呎
+(22年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
-$778万
-$26,999/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
+$774万
+$26,865/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 298呎 (1房)
-$798万
-$26,791/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
+$794万
+$26,655/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
-$813万
-$26,918/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="M23" s="20" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$819万
-$27,940/呎
-(25年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$842万
-$27,973/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
+$809万
+$26,783/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>M | 292呎 (1房)
+$814万
+$27,875/呎
+(23年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$838万
+$27,925/呎
+(21年-12月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24345,110 +24456,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$828万
-$28,837/呎
-(21年-12月-20日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
+$815万
+$28,510/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
 $1287万
-$28,227/呎
-(22年-01月-11日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
+$28,220/呎
+(23年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 333呎 (1房)
-$916万
-$27,497/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
+$927万
+$27,829/呎
+(21年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$735万
-$28,053/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$719万
-$27,146/呎
-(21年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
+$715万
+$27,306/呎
+(26年-01月-28日)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$732万
+$27,715/呎
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$800万
-$27,395/呎
-(23年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$652万
-$28,596/呎
-(22年-01月-11日)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
+$796万
+$27,259/呎
+(23年-11月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$649万
+$28,327/呎
+(21年-12月-20日)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
-$774万
-$26,865/呎
+$770万
+$26,728/呎
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$790万
+$26,434/呎
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$805万
+$26,649/呎
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$804万
+$27,424/呎
+(24年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$825万
+$27,511/呎
 (21年-12月-16日)</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$794万
-$26,655/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$809万
-$26,783/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>M | 292呎 (1房)
-$814万
-$27,875/呎
-(23年-09月-04日)</t>
-        </is>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$838万
-$27,925/呎
-(21年-12月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24456,15 +24567,15 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 $815万
 $28,510/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
 $1287万
@@ -24472,94 +24583,94 @@
 (23年-03月-20日)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
 $927万
-$27,829/呎
-(21年-12月-14日)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
+$27,913/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$715万
-$27,306/呎
-(26年-01月-27日)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
+$950万
+$36,248/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 264呎 (开放式)
 $732万
 $27,715/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$796万
-$27,259/呎
-(23年-11月-29日)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
+$752万
+$25,761/呎
+(21年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
 $649万
-$28,327/呎
-(21年-12月-19日)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
+$28,451/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
 $770万
 $26,728/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
+(21年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
 $790万
-$26,434/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
+$26,522/呎
+(21年-12月-08日)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
 $805万
 $26,649/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="M25" s="20" t="inlineStr">
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
 $804万
 $27,424/呎
-(24年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>N | 301呎 (1房)
 $825万
-$27,511/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
+$27,420/呎
+(21年-12月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24567,110 +24678,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
-$815万
-$28,510/呎
+$807万
+$28,227/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1311万
+$28,747/呎
+(23年-04月-12日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 333呎 (1房)
+$908万
+$27,254/呎
+(24年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$701万
+$26,766/呎
+(26年-01月-29日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
+$724万
+$27,336/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$761万
+$26,072/呎
+(21年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$628万
+$27,436/呎
+(23年-05月-10日)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$762万
+$26,462/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 298呎 (1房)
+$782万
+$26,257/呎
+(21年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$797万
+$26,384/呎
 (21年-12月-16日)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1287万
-$28,220/呎
-(23年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$927万
-$27,913/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$950万
-$36,248/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$732万
-$27,715/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$752万
-$25,761/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$649万
-$28,451/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$770万
-$26,728/呎
-(21年-12月-14日)</t>
-        </is>
-      </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$790万
-$26,522/呎
-(21年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$805万
-$26,649/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
-$804万
-$27,424/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
+$799万
+$27,258/呎
+(24年-05月-09日)</t>
+        </is>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>N | 301呎 (1房)
-$825万
-$27,420/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+$817万
+$27,148/呎
+(21年-12月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24678,110 +24789,221 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
-$807万
-$28,227/呎
+$804万
+$28,118/呎
+(21年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 456呎 (2房)
+$1265万
+$27,739/呎
+(23年-03月-17日)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 332呎 (1房)
+$914万
+$27,533/呎
+(22年-01月-13日)</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>E | 262呎 (开放式)
+$948万
+$36,198/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 264呎 (开放式)
+$721万
+$27,300/呎
+(22年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 292呎 (1房)
+$758万
+$25,942/呎
+(21年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 229呎 (开放式)
+$638万
+$27,881/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 288呎 (1房)
+$742万
+$25,759/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$762万
+$25,474/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>L | 302呎 (1房)
+$793万
+$26,253/呎
 (21年-12月-16日)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>M | 293呎 (1房)
+$810万
+$27,631/呎
+(24年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$813万
+$27,100/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 260呎 (开放式)
+$724万
+$27,838/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 287呎 (1房)
+$781万
+$27,226/呎
+(21年-12月-22日)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 456呎 (2房)
-$1311万
-$28,747/呎
-(23年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
+$1248万
+$27,368/呎
+(22年-01月-17日)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 333呎 (1房)
-$908万
-$27,254/呎
-(24年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
+$898万
+$26,981/呎
+(21年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
+$709万
+$27,063/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (开放式)
 $701万
-$26,766/呎
-(26年-01月-28日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$724万
-$27,336/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
+$26,446/呎
+(25年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 292呎 (1房)
-$761万
-$26,072/呎
+$753万
+$25,785/呎
 (21年-12月-14日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$628万
-$27,436/呎
-(23年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 228呎 (开放式)
+$635万
+$27,834/呎
+(22年-09月-20日)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 288呎 (1房)
-$762万
-$26,462/呎
+$754万
+$26,172/呎
 (21年-12月-09日)</t>
         </is>
       </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>K | 298呎 (1房)
-$782万
-$26,257/呎
-(21年-12月-16日)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>K | 299呎 (1房)
+$757万
+$25,320/呎
+(21年-12月-10日)</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>L | 302呎 (1房)
-$797万
-$26,384/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="M27" s="20" t="inlineStr">
+$788万
+$26,095/呎
+(21年-12月-13日)</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
         <is>
           <t>M | 293呎 (1房)
-$799万
-$27,258/呎
-(24年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
-        <is>
-          <t>N | 301呎 (1房)
-$817万
-$27,148/呎
-(21年-12月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
+$794万
+$27,095/呎
+(25年-09月-05日)</t>
+        </is>
+      </c>
+      <c r="N29" s="20" t="inlineStr">
+        <is>
+          <t>N | 300呎 (1房)
+$809万
+$26,965/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 260呎 (开放式)
 -
@@ -24789,234 +25011,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
-$804万
-$28,118/呎
-(21年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1265万
-$27,739/呎
-(23年-03月-16日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 332呎 (1房)
-$914万
-$27,533/呎
-(22年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$948万
-$36,198/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 264呎 (开放式)
-$721万
-$27,300/呎
-(22年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$758万
-$25,942/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>H | 229呎 (开放式)
-$638万
-$27,881/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$742万
-$25,759/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="K28" s="20" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$762万
-$25,474/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$793万
-$26,253/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="M28" s="20" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$810万
-$27,631/呎
-(24年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$813万
-$27,100/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
-$724万
-$27,838/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 287呎 (1房)
-$781万
-$27,226/呎
-(21年-12月-21日)</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>C | 456呎 (2房)
-$1248万
-$27,368/呎
-(22年-01月-16日)</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>D | 333呎 (1房)
-$898万
-$26,981/呎
-(21年-12月-15日)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>E | 262呎 (开放式)
-$709万
-$27,063/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>F | 265呎 (开放式)
-$701万
-$26,446/呎
-(25年-12月-11日)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>G | 292呎 (1房)
-$753万
-$25,785/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>H | 228呎 (开放式)
-$635万
-$27,834/呎
-(22年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>J | 288呎 (1房)
-$754万
-$26,172/呎
-(21年-12月-08日)</t>
-        </is>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>K | 299呎 (1房)
-$757万
-$25,320/呎
-(21年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>L | 302呎 (1房)
-$788万
-$26,095/呎
-(21年-12月-12日)</t>
-        </is>
-      </c>
-      <c r="M29" s="20" t="inlineStr">
-        <is>
-          <t>M | 293呎 (1房)
-$794万
-$27,095/呎
-(25年-09月-04日)</t>
-        </is>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
-        <is>
-          <t>N | 300呎 (1房)
-$809万
-$26,965/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>A | 260呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 $778万
 $27,217/呎
-(22年-01月-12日)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -25024,7 +25024,7 @@
           <t>C | 456呎 (2房)
 $1248万
 $27,365/呎
-(23年-06月-18日)</t>
+(23年-06月-19日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -25032,7 +25032,7 @@
           <t>D | 333呎 (1房)
 $894万
 $26,846/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -25040,7 +25040,7 @@
           <t>E | 262呎 (开放式)
 $690万
 $26,340/呎
-(23年-08月-10日)</t>
+(23年-08月-11日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -25048,7 +25048,7 @@
           <t>F | 265呎 (开放式)
 $697万
 $26,314/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -25056,7 +25056,7 @@
           <t>G | 292呎 (1房)
 $750万
 $25,675/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -25064,7 +25064,7 @@
           <t>H | 229呎 (开放式)
 $632万
 $27,600/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -25072,7 +25072,7 @@
           <t>J | 288呎 (1房)
 $750万
 $26,041/呎
-(21年-12月-14日)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -25080,7 +25080,7 @@
           <t>K | 298呎 (1房)
 $770万
 $25,840/呎
-(21年-12月-21日)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="L30" s="20" t="inlineStr">
@@ -25088,7 +25088,7 @@
           <t>L | 302呎 (1房)
 $784万
 $25,964/呎
-(21年-12月-08日)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr">
@@ -25096,7 +25096,7 @@
           <t>M | 293呎 (1房)
 $792万
 $27,015/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -25104,7 +25104,7 @@
           <t>N | 300呎 (1房)
 $805万
 $26,830/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
           <t>C | 309呎 (1房)
 $947万
 $30,638/呎
-(23年-03月-02日)</t>
+(23年-03月-03日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -25143,15 +25143,15 @@
           <t>D | 240呎 (开放式)
 $756万
 $31,502/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>E | 243呎 (开放式)
+          <t>E | 242呎 (开放式)
 $804万
-$33,100/呎
-(26年-06月-24日)</t>
+$33,236/呎
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -25159,7 +25159,7 @@
           <t>F | 270呎 (1房)
 $814万
 $30,130/呎
-(21年-12月-16日)</t>
+(21年-12月-17日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -25167,7 +25167,7 @@
           <t>G | 207呎 (开放式)
 $637万
 $30,765/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -25175,7 +25175,7 @@
           <t>H | 267呎 (1房)
 $763万
 $28,561/呎
-(21年-12月-07日)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -25183,7 +25183,7 @@
           <t>J | 278呎 (1房)
 $802万
 $28,861/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -25191,7 +25191,7 @@
           <t>K | 279呎 (1房)
 $859万
 $30,799/呎
-(21年-12月-15日)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="L31" s="20" t="inlineStr">
@@ -25199,7 +25199,7 @@
           <t>L | 271呎 (1房)
 $964万
 $35,587/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr">
@@ -25207,7 +25207,7 @@
           <t>M | 279呎 (1房)
 $904万
 $32,400/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr"/>

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>7637400</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>28930</v>
+        <v>28820</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>7637400</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>28930</v>
+        <v>28820</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -23602,9 +23602,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 264呎 (开放式)
+          <t>F | 265呎 (开放式)
 $764万
-$28,930/呎
+$28,820/呎
 (21年-12月-10日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -16680,7 +16680,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>7903700</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>26434</v>
+        <v>26522</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>7903700</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>26434</v>
+        <v>26522</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -24522,9 +24522,9 @@
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>K | 299呎 (1房)
+          <t>K | 298呎 (1房)
 $790万
-$26,434/呎
+$26,522/呎
 (21年-12月-08日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -5598,23 +5598,23 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>9654000</v>
+        <v>8688600</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>36847</v>
+        <v>33163</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="5" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -22189,7 +22189,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -22926,12 +22926,12 @@
 (21年-12月-14日)</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$965万
-$36,847/呎
-(在售)</t>
+$869万
+$33,163/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
